--- a/engagement_survey_forms/003_managerial_communication_effectiveness_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/003_managerial_communication_effectiveness_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'options':_[{'id':_1,_'name':_'very_good'},_{'id':_2,_'name':_'good'},_{'id':_3,_'name':_'fair'},_{'id':_4,_'name':_'poor'},_{'id':_5,_'name':_'very_poor'},_{'id':_6,_'name':_"don't_know"}],_'hint':_none}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'options': [{'id': 1, 'name': 'Very Good'}, {'id': 2, 'name': 'Good'}, {'id': 3, 'name': 'Fair'}, {'id': 4, 'name': 'Poor'}, {'id': 5, 'name': 'Very Poor'}, {'id': 6, 'name': "Don't Know"}], 'hint': None}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'options':_[{'id':_1,_'name':_'email'},_{'id':_2,_'name':_'phone'},_{'id':_3,_'name':_'in_person'},_{'id':_4,_'name':_'video_conference'},_{'id':_5,_'name':_'chat'},_{'id':_6,_'name':_"don't_know"}],_'hint':_none}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'options': [{'id': 1, 'name': 'Email'}, {'id': 2, 'name': 'Phone'}, {'id': 3, 'name': 'In person'}, {'id': 4, 'name': 'Video Conference'}, {'id': 5, 'name': 'Chat'}, {'id': 6, 'name': "Don't Know"}], 'hint': None}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'options':_[{'id':_1,_'name':_'daily'},_{'id':_2,_'name':_'weekly'},_{'id':_3,_'name':_'monthly'},_{'id':_4,_'name':_'rarely'}],_'hint':_none}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'options': [{'id': 1, 'name': 'Daily'}, {'id': 2, 'name': 'Weekly'}, {'id': 3, 'name': 'Monthly'}, {'id': 4, 'name': 'Rarely'}], 'hint': None}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
